--- a/data_cleaned/clean_exchange_rate_2004_2024.xlsx
+++ b/data_cleaned/clean_exchange_rate_2004_2024.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C245"/>
+  <dimension ref="A1:C253"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3143,469 +3143,573 @@
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
-        <v>44562</v>
+        <v>44317</v>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>2022-01</t>
+          <t>2021-05</t>
         </is>
       </c>
       <c r="C210" t="n">
-        <v>414.535</v>
+        <v>397.1458333333333</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
-        <v>44593</v>
+        <v>44348</v>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>2022-02</t>
+          <t>2021-06</t>
         </is>
       </c>
       <c r="C211" t="n">
-        <v>416.149</v>
+        <v>409.664761904762</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
-        <v>44621</v>
+        <v>44378</v>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>2022-03</t>
+          <t>2021-07</t>
         </is>
       </c>
       <c r="C212" t="n">
-        <v>415.8273913043478</v>
+        <v>409.6326315789474</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
-        <v>44652</v>
+        <v>44409</v>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>2022-04</t>
+          <t>2021-08</t>
         </is>
       </c>
       <c r="C213" t="n">
-        <v>415.4015789473684</v>
+        <v>409.6531818181818</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
-        <v>44682</v>
+        <v>44440</v>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>2022-05</t>
+          <t>2021-09</t>
         </is>
       </c>
       <c r="C214" t="n">
-        <v>415.075165</v>
+        <v>410.0168181818182</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
-        <v>44713</v>
+        <v>44470</v>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>2022-06</t>
+          <t>2021-10</t>
         </is>
       </c>
       <c r="C215" t="n">
-        <v>415.0247619047619</v>
+        <v>410.4126315789474</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
-        <v>44743</v>
+        <v>44501</v>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>2022-07</t>
+          <t>2021-11</t>
         </is>
       </c>
       <c r="C216" t="n">
-        <v>415.1052631578947</v>
+        <v>410.8054545454545</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
-        <v>44774</v>
+        <v>44531</v>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>2022-08</t>
+          <t>2021-12</t>
         </is>
       </c>
       <c r="C217" t="n">
-        <v>419.9727272727272</v>
+        <v>411.1328571428572</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
-        <v>44805</v>
+        <v>44562</v>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>2022-09</t>
+          <t>2022-01</t>
         </is>
       </c>
       <c r="C218" t="n">
-        <v>428.7495238095238</v>
+        <v>414.535</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
-        <v>44835</v>
+        <v>44593</v>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>2022-10</t>
+          <t>2022-02</t>
         </is>
       </c>
       <c r="C219" t="n">
-        <v>436.1155555555555</v>
+        <v>416.149</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
-        <v>44866</v>
+        <v>44621</v>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>2022-11</t>
+          <t>2022-03</t>
         </is>
       </c>
       <c r="C220" t="n">
-        <v>441.8792727272727</v>
+        <v>415.8273913043478</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
-        <v>44896</v>
+        <v>44652</v>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>2022-12</t>
+          <t>2022-04</t>
         </is>
       </c>
       <c r="C221" t="n">
-        <v>445.9705</v>
+        <v>415.4015789473684</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
-        <v>44927</v>
+        <v>44682</v>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>2023-01</t>
+          <t>2022-05</t>
         </is>
       </c>
       <c r="C222" t="n">
-        <v>454.9704761904762</v>
+        <v>415.075165</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
-        <v>44958</v>
+        <v>44713</v>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>2023-02</t>
+          <t>2022-06</t>
         </is>
       </c>
       <c r="C223" t="n">
-        <v>460.426</v>
+        <v>415.0247619047619</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
-        <v>44986</v>
+        <v>44743</v>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>2023-03</t>
+          <t>2022-07</t>
         </is>
       </c>
       <c r="C224" t="n">
-        <v>460.4313636363636</v>
+        <v>415.1052631578947</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
-        <v>45017</v>
+        <v>44774</v>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>2023-04</t>
+          <t>2022-08</t>
         </is>
       </c>
       <c r="C225" t="n">
-        <v>460.4175</v>
+        <v>419.9727272727272</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
-        <v>45047</v>
+        <v>44805</v>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>2023-05</t>
+          <t>2022-09</t>
         </is>
       </c>
       <c r="C226" t="n">
-        <v>460.702380952381</v>
+        <v>428.7495238095238</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
-        <v>45078</v>
+        <v>44835</v>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>2023-06</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="C227" t="n">
-        <v>607.7488888888888</v>
+        <v>436.1155555555555</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
-        <v>45108</v>
+        <v>44866</v>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>2023-07</t>
+          <t>2022-11</t>
         </is>
       </c>
       <c r="C228" t="n">
-        <v>769.8165238095238</v>
+        <v>441.8792727272727</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
-        <v>45139</v>
+        <v>44896</v>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>2023-08</t>
+          <t>2022-12</t>
         </is>
       </c>
       <c r="C229" t="n">
-        <v>761.6203478260869</v>
+        <v>445.9705</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
-        <v>45170</v>
+        <v>44927</v>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>2023-09</t>
+          <t>2023-01</t>
         </is>
       </c>
       <c r="C230" t="n">
-        <v>761.3271578947368</v>
+        <v>454.9704761904762</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
-        <v>45200</v>
+        <v>44958</v>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>2023-10</t>
+          <t>2023-02</t>
         </is>
       </c>
       <c r="C231" t="n">
-        <v>796.438</v>
+        <v>460.426</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
-        <v>45231</v>
+        <v>44986</v>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>2023-11</t>
+          <t>2023-03</t>
         </is>
       </c>
       <c r="C232" t="n">
-        <v>832.6758095238094</v>
+        <v>460.4313636363636</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
-        <v>45261</v>
+        <v>45017</v>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>2023-12</t>
+          <t>2023-04</t>
         </is>
       </c>
       <c r="C233" t="n">
-        <v>898.8976315789474</v>
+        <v>460.4175</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
-        <v>45292</v>
+        <v>45047</v>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2023-05</t>
         </is>
       </c>
       <c r="C234" t="n">
-        <v>941.2560227272727</v>
+        <v>460.702380952381</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
-        <v>45323</v>
+        <v>45078</v>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2023-06</t>
         </is>
       </c>
       <c r="C235" t="n">
-        <v>1504.820523809524</v>
+        <v>607.7488888888888</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
-        <v>45352</v>
+        <v>45108</v>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2023-07</t>
         </is>
       </c>
       <c r="C236" t="n">
-        <v>1510.8432</v>
+        <v>769.8165238095238</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
-        <v>45383</v>
+        <v>45139</v>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2023-08</t>
         </is>
       </c>
       <c r="C237" t="n">
-        <v>1236.557722222222</v>
+        <v>761.6203478260869</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
-        <v>45413</v>
+        <v>45170</v>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2023-09</t>
         </is>
       </c>
       <c r="C238" t="n">
-        <v>1435.567818181818</v>
+        <v>761.3271578947368</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
-        <v>45444</v>
+        <v>45200</v>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2023-10</t>
         </is>
       </c>
       <c r="C239" t="n">
-        <v>1481.766235294117</v>
+        <v>796.438</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
-        <v>45474</v>
+        <v>45231</v>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2023-11</t>
         </is>
       </c>
       <c r="C240" t="n">
-        <v>1557.570125</v>
+        <v>832.6758095238094</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
-        <v>45505</v>
+        <v>45261</v>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2023-12</t>
         </is>
       </c>
       <c r="C241" t="n">
-        <v>1586.939454545455</v>
+        <v>898.8976315789474</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
-        <v>45536</v>
+        <v>45292</v>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2024-01</t>
         </is>
       </c>
       <c r="C242" t="n">
-        <v>1617.7167</v>
+        <v>941.2560227272727</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
-        <v>45566</v>
+        <v>45323</v>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2024-02</t>
         </is>
       </c>
       <c r="C243" t="n">
-        <v>1640.663863636364</v>
+        <v>1504.820523809524</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
-        <v>45597</v>
+        <v>45352</v>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2024-03</t>
         </is>
       </c>
       <c r="C244" t="n">
-        <v>1670.276428571429</v>
+        <v>1510.8432</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
+        <v>45383</v>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>2024-04</t>
+        </is>
+      </c>
+      <c r="C245" t="n">
+        <v>1236.557722222222</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="1" t="n">
+        <v>45413</v>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>2024-05</t>
+        </is>
+      </c>
+      <c r="C246" t="n">
+        <v>1435.567818181818</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="1" t="n">
+        <v>45444</v>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>2024-06</t>
+        </is>
+      </c>
+      <c r="C247" t="n">
+        <v>1481.766235294117</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="1" t="n">
+        <v>45474</v>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>2024-07</t>
+        </is>
+      </c>
+      <c r="C248" t="n">
+        <v>1557.570125</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="1" t="n">
+        <v>45505</v>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>2024-08</t>
+        </is>
+      </c>
+      <c r="C249" t="n">
+        <v>1586.939454545455</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="1" t="n">
+        <v>45536</v>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>2024-09</t>
+        </is>
+      </c>
+      <c r="C250" t="n">
+        <v>1617.7167</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="1" t="n">
+        <v>45566</v>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>2024-10</t>
+        </is>
+      </c>
+      <c r="C251" t="n">
+        <v>1640.663863636364</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="1" t="n">
+        <v>45597</v>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>2024-11</t>
+        </is>
+      </c>
+      <c r="C252" t="n">
+        <v>1670.276428571429</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="1" t="n">
         <v>45627</v>
       </c>
-      <c r="B245" t="inlineStr">
+      <c r="B253" t="inlineStr">
         <is>
           <t>2024-12</t>
         </is>
       </c>
-      <c r="C245" t="n">
+      <c r="C253" t="n">
         <v>1553.253995</v>
       </c>
     </row>
